--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>93.57279327168455</v>
+        <v>15.20557890664874</v>
       </c>
       <c r="D2" t="n">
-        <v>38.02807249642863</v>
+        <v>6.179561780669652</v>
       </c>
       <c r="E2" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F2" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>83.74784376055801</v>
+        <v>13.60902461109068</v>
       </c>
       <c r="D3" t="n">
-        <v>31.19565828406773</v>
+        <v>5.069294471161006</v>
       </c>
       <c r="E3" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F3" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>112.8869062022436</v>
+        <v>18.34412225786458</v>
       </c>
       <c r="D4" t="n">
-        <v>66.89196306150852</v>
+        <v>10.86994399749513</v>
       </c>
       <c r="E4" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F4" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>85.87188200544803</v>
+        <v>13.95418082588531</v>
       </c>
       <c r="D5" t="n">
-        <v>48.01097087228838</v>
+        <v>7.801782766746861</v>
       </c>
       <c r="E5" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F5" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>87.2979785357534</v>
+        <v>14.18592151205993</v>
       </c>
       <c r="D6" t="n">
-        <v>32.82553862863097</v>
+        <v>5.334150027152532</v>
       </c>
       <c r="E6" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F6" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>75.63403635621448</v>
+        <v>12.29053090788485</v>
       </c>
       <c r="D7" t="n">
-        <v>36.46383835665745</v>
+        <v>5.925373732956837</v>
       </c>
       <c r="E7" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F7" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>68.96141744118475</v>
+        <v>11.20623033419252</v>
       </c>
       <c r="D8" t="n">
-        <v>16.47657007265104</v>
+        <v>2.677442636805794</v>
       </c>
       <c r="E8" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F8" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>65.3326478409565</v>
+        <v>10.61655527415543</v>
       </c>
       <c r="D9" t="n">
-        <v>31.03718140636586</v>
+        <v>5.043541978534453</v>
       </c>
       <c r="E9" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F9" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>66.50365596336623</v>
+        <v>10.80684409404701</v>
       </c>
       <c r="D10" t="n">
-        <v>35.65459297201414</v>
+        <v>5.793871357952297</v>
       </c>
       <c r="E10" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F10" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>72.90062138415681</v>
+        <v>11.84635097492548</v>
       </c>
       <c r="D11" t="n">
-        <v>19.51417457947282</v>
+        <v>3.171053369164334</v>
       </c>
       <c r="E11" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F11" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>69.09917332967972</v>
+        <v>11.22861566607295</v>
       </c>
       <c r="D12" t="n">
-        <v>33.63406011768428</v>
+        <v>5.465534769123695</v>
       </c>
       <c r="E12" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F12" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>73.85502909495786</v>
+        <v>12.00144222793065</v>
       </c>
       <c r="D13" t="n">
-        <v>32.35440260735881</v>
+        <v>5.257590423695808</v>
       </c>
       <c r="E13" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F13" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>83.96812254822831</v>
+        <v>13.6448199140871</v>
       </c>
       <c r="D14" t="n">
-        <v>29.59139370355065</v>
+        <v>4.808601476826982</v>
       </c>
       <c r="E14" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F14" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>89.57671984011175</v>
+        <v>14.55621697401816</v>
       </c>
       <c r="D15" t="n">
-        <v>43.45511788363554</v>
+        <v>7.061456656090775</v>
       </c>
       <c r="E15" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F15" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>69.74788783403787</v>
+        <v>11.33403177303115</v>
       </c>
       <c r="D16" t="n">
-        <v>14.0313075945469</v>
+        <v>2.280087484113871</v>
       </c>
       <c r="E16" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F16" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>59.18876115189924</v>
+        <v>9.618173687183628</v>
       </c>
       <c r="D17" t="n">
-        <v>31.52339536927614</v>
+        <v>5.122551747507372</v>
       </c>
       <c r="E17" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F17" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>74.65980312575113</v>
+        <v>12.13221800793456</v>
       </c>
       <c r="D18" t="n">
-        <v>30.28247368273733</v>
+        <v>4.920901973444817</v>
       </c>
       <c r="E18" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F18" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>99.21032235165943</v>
+        <v>16.12167738214466</v>
       </c>
       <c r="D19" t="n">
-        <v>53.56641775507404</v>
+        <v>8.704542885199531</v>
       </c>
       <c r="E19" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F19" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>57.65114615355956</v>
+        <v>9.368311249953429</v>
       </c>
       <c r="D20" t="n">
-        <v>23.30772404161333</v>
+        <v>3.787505156762166</v>
       </c>
       <c r="E20" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F20" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>52.49363355703635</v>
+        <v>8.530215453018407</v>
       </c>
       <c r="D21" t="n">
-        <v>1.471864718383907</v>
+        <v>0.239178016737385</v>
       </c>
       <c r="E21" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F21" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>79.90499667244805</v>
+        <v>12.98456195927281</v>
       </c>
       <c r="D22" t="n">
-        <v>34.23545274315833</v>
+        <v>5.563261070763228</v>
       </c>
       <c r="E22" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F22" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>66.76840605369115</v>
+        <v>10.84986598372481</v>
       </c>
       <c r="D23" t="n">
-        <v>20.64407766989304</v>
+        <v>3.354662621357619</v>
       </c>
       <c r="E23" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F23" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>65.38877279348634</v>
+        <v>10.62567557894153</v>
       </c>
       <c r="D24" t="n">
-        <v>16.90873696986968</v>
+        <v>2.747669757603823</v>
       </c>
       <c r="E24" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F24" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>72.59915515451924</v>
+        <v>11.79736271260938</v>
       </c>
       <c r="D25" t="n">
-        <v>26.544527606094</v>
+        <v>4.313485735990276</v>
       </c>
       <c r="E25" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F25" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>78.58379540885456</v>
+        <v>12.76986675393887</v>
       </c>
       <c r="D26" t="n">
-        <v>36.16973873281365</v>
+        <v>5.877582544082218</v>
       </c>
       <c r="E26" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F26" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>44.83058868570219</v>
+        <v>7.284970661426606</v>
       </c>
       <c r="D27" t="n">
-        <v>11.32366834655315</v>
+        <v>1.840096106314887</v>
       </c>
       <c r="E27" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F27" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>34.88807730464381</v>
+        <v>5.669312562004619</v>
       </c>
       <c r="D28" t="n">
-        <v>18.02579542680962</v>
+        <v>2.929191756856563</v>
       </c>
       <c r="E28" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F28" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>65.61498120745786</v>
+        <v>10.6624344462119</v>
       </c>
       <c r="D29" t="n">
-        <v>32.69491964104293</v>
+        <v>5.312924441669476</v>
       </c>
       <c r="E29" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F29" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>52.15255462820596</v>
+        <v>8.474790127083468</v>
       </c>
       <c r="D30" t="n">
-        <v>21.7753149197963</v>
+        <v>3.5384886744669</v>
       </c>
       <c r="E30" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F30" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>16.69923611687033</v>
+        <v>2.713625868991429</v>
       </c>
       <c r="D31" t="n">
-        <v>23.53905379892328</v>
+        <v>3.825096242325033</v>
       </c>
       <c r="E31" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F31" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>32.47870535531017</v>
+        <v>5.277789620237902</v>
       </c>
       <c r="D32" t="n">
-        <v>25.30207678493684</v>
+        <v>4.111587477552237</v>
       </c>
       <c r="E32" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F32" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>73.25459328071084</v>
+        <v>11.90387140811551</v>
       </c>
       <c r="D33" t="n">
-        <v>42.71085431636008</v>
+        <v>6.940513826408514</v>
       </c>
       <c r="E33" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F33" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>23.99300861223192</v>
+        <v>3.898863899487687</v>
       </c>
       <c r="D34" t="n">
-        <v>25.61247957150794</v>
+        <v>4.162027930370041</v>
       </c>
       <c r="E34" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F34" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>10.44117005125333</v>
+        <v>1.696690133328666</v>
       </c>
       <c r="D35" t="n">
-        <v>15.06147701165951</v>
+        <v>2.44749001439467</v>
       </c>
       <c r="E35" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F35" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>37.84400510915475</v>
+        <v>6.149650830237647</v>
       </c>
       <c r="D36" t="n">
-        <v>21.31234792818214</v>
+        <v>3.463256538329598</v>
       </c>
       <c r="E36" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F36" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>54.41273068956501</v>
+        <v>8.842068737054314</v>
       </c>
       <c r="D37" t="n">
-        <v>23.47657732500482</v>
+        <v>3.814943815313283</v>
       </c>
       <c r="E37" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F37" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>81.53254782269541</v>
+        <v>13.249039021188</v>
       </c>
       <c r="D38" t="n">
-        <v>51.24708217718447</v>
+        <v>8.327650853792477</v>
       </c>
       <c r="E38" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F38" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>48.65627875254565</v>
+        <v>7.906645297288668</v>
       </c>
       <c r="D39" t="n">
-        <v>45.77468020143958</v>
+        <v>7.438385532733932</v>
       </c>
       <c r="E39" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F39" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>74.68577907398476</v>
+        <v>12.13643909952252</v>
       </c>
       <c r="D40" t="n">
-        <v>45.69629278129813</v>
+        <v>7.425647576960945</v>
       </c>
       <c r="E40" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F40" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>59.56769164875421</v>
+        <v>9.679749892922558</v>
       </c>
       <c r="D41" t="n">
-        <v>32.35578780270602</v>
+        <v>5.257815517939728</v>
       </c>
       <c r="E41" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F41" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>24.14674515161932</v>
+        <v>3.923846087138139</v>
       </c>
       <c r="D42" t="n">
-        <v>21.7286089783918</v>
+        <v>3.530898958988668</v>
       </c>
       <c r="E42" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F42" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>17.00896022996415</v>
+        <v>2.763956037369174</v>
       </c>
       <c r="D43" t="n">
-        <v>13.79219412788152</v>
+        <v>2.241231545780747</v>
       </c>
       <c r="E43" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F43" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>34.94855925088299</v>
+        <v>5.679140878268486</v>
       </c>
       <c r="D44" t="n">
-        <v>17.8033948578288</v>
+        <v>2.893051664397181</v>
       </c>
       <c r="E44" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F44" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>65.41120018206544</v>
+        <v>10.62932002958564</v>
       </c>
       <c r="D45" t="n">
-        <v>58.27284994171102</v>
+        <v>9.469338115528041</v>
       </c>
       <c r="E45" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F45" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>55.52133991492183</v>
+        <v>9.022217736174799</v>
       </c>
       <c r="D46" t="n">
-        <v>54.14541773590418</v>
+        <v>8.798630382084429</v>
       </c>
       <c r="E46" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F46" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>30.34322969967591</v>
+        <v>4.930774826197336</v>
       </c>
       <c r="D47" t="n">
-        <v>27.08743803695386</v>
+        <v>4.401708681005002</v>
       </c>
       <c r="E47" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F47" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>43.75367954433583</v>
+        <v>7.109972925954573</v>
       </c>
       <c r="D48" t="n">
-        <v>26.06088023992486</v>
+        <v>4.23489303898779</v>
       </c>
       <c r="E48" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F48" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>52.87575681344092</v>
+        <v>8.59231048218415</v>
       </c>
       <c r="D49" t="n">
-        <v>50.46080683878696</v>
+        <v>8.199881111302881</v>
       </c>
       <c r="E49" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F49" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>24.87283338377593</v>
+        <v>4.041835424863589</v>
       </c>
       <c r="D50" t="n">
-        <v>20.54197698985398</v>
+        <v>3.338071260851272</v>
       </c>
       <c r="E50" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F50" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>68.00142191105269</v>
+        <v>11.05023106054606</v>
       </c>
       <c r="D51" t="n">
-        <v>45.57819530739612</v>
+        <v>7.40645673745187</v>
       </c>
       <c r="E51" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F51" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>32.53605070367644</v>
+        <v>5.287108239347421</v>
       </c>
       <c r="D52" t="n">
-        <v>27.83764893115864</v>
+        <v>4.523617951313279</v>
       </c>
       <c r="E52" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F52" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>26.37920677022008</v>
+        <v>4.286621100160763</v>
       </c>
       <c r="D53" t="n">
-        <v>5.063241222696965</v>
+        <v>0.8227766986882569</v>
       </c>
       <c r="E53" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F53" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>40.22654079880559</v>
+        <v>6.536812879805908</v>
       </c>
       <c r="D54" t="n">
-        <v>37.98370654030517</v>
+        <v>6.172352312799591</v>
       </c>
       <c r="E54" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F54" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>14.9366699039666</v>
+        <v>2.427208859394572</v>
       </c>
       <c r="D55" t="n">
-        <v>8.516056583941182</v>
+        <v>1.383859194890442</v>
       </c>
       <c r="E55" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F55" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>51.06769029585936</v>
+        <v>8.298499673077146</v>
       </c>
       <c r="D56" t="n">
-        <v>30.77249064595773</v>
+        <v>5.000529729968131</v>
       </c>
       <c r="E56" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F56" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>83.798809302395</v>
+        <v>13.61730651163919</v>
       </c>
       <c r="D57" t="n">
-        <v>60.31669083158169</v>
+        <v>9.801462260132025</v>
       </c>
       <c r="E57" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F57" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>88.03995138497476</v>
+        <v>14.3064921000584</v>
       </c>
       <c r="D58" t="n">
-        <v>65.9327967768396</v>
+        <v>10.71407947623644</v>
       </c>
       <c r="E58" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F58" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>51.76118958007815</v>
+        <v>8.4111933067627</v>
       </c>
       <c r="D59" t="n">
-        <v>46.93748717314381</v>
+        <v>7.627341665635869</v>
       </c>
       <c r="E59" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F59" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>45.26571043438766</v>
+        <v>7.355677945587995</v>
       </c>
       <c r="D60" t="n">
-        <v>39.9051784082517</v>
+        <v>6.484591491340901</v>
       </c>
       <c r="E60" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F60" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>37.1241494630368</v>
+        <v>6.032674287743481</v>
       </c>
       <c r="D61" t="n">
-        <v>16.66999966673331</v>
+        <v>2.708874945844164</v>
       </c>
       <c r="E61" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F61" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>42.7377638768557</v>
+        <v>6.944886629989051</v>
       </c>
       <c r="D62" t="n">
-        <v>36.76727663874365</v>
+        <v>5.974682453795842</v>
       </c>
       <c r="E62" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F62" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>33.36465527124943</v>
+        <v>5.421756481578033</v>
       </c>
       <c r="D63" t="n">
-        <v>25.3525628720295</v>
+        <v>4.119791466704793</v>
       </c>
       <c r="E63" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F63" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>36.15281165923007</v>
+        <v>5.874831894624887</v>
       </c>
       <c r="D64" t="n">
-        <v>22.939534045447</v>
+        <v>3.727674282385137</v>
       </c>
       <c r="E64" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F64" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>80.41182639616508</v>
+        <v>13.06692178937683</v>
       </c>
       <c r="D65" t="n">
-        <v>59.7417993218</v>
+        <v>9.708042389792501</v>
       </c>
       <c r="E65" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F65" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2528,16 +2528,16 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>50.91868937378641</v>
+        <v>8.274287023240293</v>
       </c>
       <c r="D66" t="n">
-        <v>45.14726657670658</v>
+        <v>7.33643081871482</v>
       </c>
       <c r="E66" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F66" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>62.71734422876954</v>
+        <v>10.19156843717505</v>
       </c>
       <c r="D67" t="n">
-        <v>57.80524264595866</v>
+        <v>9.393351929968283</v>
       </c>
       <c r="E67" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F67" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2592,16 +2592,16 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>68.0643910528607</v>
+        <v>11.06046354608986</v>
       </c>
       <c r="D68" t="n">
-        <v>63.43637409542045</v>
+        <v>10.30841079050582</v>
       </c>
       <c r="E68" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F68" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2624,16 +2624,16 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>59.69767421436757</v>
+        <v>9.700872059834731</v>
       </c>
       <c r="D69" t="n">
-        <v>36.73153854708895</v>
+        <v>5.968875013901955</v>
       </c>
       <c r="E69" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F69" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>83.92523748207937</v>
+        <v>13.6378510908379</v>
       </c>
       <c r="D70" t="n">
-        <v>62.44080099159702</v>
+        <v>10.14663016113452</v>
       </c>
       <c r="E70" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F70" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2688,16 +2688,16 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>76.52085922216433</v>
+        <v>12.4346396236017</v>
       </c>
       <c r="D71" t="n">
-        <v>72.36877464006365</v>
+        <v>11.75992587901034</v>
       </c>
       <c r="E71" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F71" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2720,16 +2720,16 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>50.91005749232717</v>
+        <v>8.272884342503165</v>
       </c>
       <c r="D72" t="n">
-        <v>44.3794913820716</v>
+        <v>7.211667349586635</v>
       </c>
       <c r="E72" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F72" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2752,16 +2752,16 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>57.98519244368202</v>
+        <v>9.422593772098327</v>
       </c>
       <c r="D73" t="n">
-        <v>51.91678027085536</v>
+        <v>8.436476794013997</v>
       </c>
       <c r="E73" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F73" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2784,16 +2784,16 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>55.20077794243594</v>
+        <v>8.97012641564584</v>
       </c>
       <c r="D74" t="n">
-        <v>32.48708987762149</v>
+        <v>5.279152105113492</v>
       </c>
       <c r="E74" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F74" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="n">
-        <v>48.72764111578008</v>
+        <v>7.918241681314264</v>
       </c>
       <c r="D75" t="n">
-        <v>37.95091173330212</v>
+        <v>6.167023156661595</v>
       </c>
       <c r="E75" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F75" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>59.81677941430694</v>
+        <v>9.720226654824879</v>
       </c>
       <c r="D76" t="n">
-        <v>53.4794876149411</v>
+        <v>8.690416737427929</v>
       </c>
       <c r="E76" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F76" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2880,16 +2880,16 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>54.2628012496224</v>
+        <v>8.817705203063641</v>
       </c>
       <c r="D77" t="n">
-        <v>34.30622621456131</v>
+        <v>5.574761759866212</v>
       </c>
       <c r="E77" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F77" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2912,16 +2912,16 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>50.38532283255277</v>
+        <v>8.187614960289824</v>
       </c>
       <c r="D78" t="n">
-        <v>33.95814819431018</v>
+        <v>5.518199081575404</v>
       </c>
       <c r="E78" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F78" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2944,16 +2944,16 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>58.85537972875196</v>
+        <v>9.563999205922194</v>
       </c>
       <c r="D79" t="n">
-        <v>37.56512862867488</v>
+        <v>6.104333402159668</v>
       </c>
       <c r="E79" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F79" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2976,16 +2976,16 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>56.08082842382991</v>
+        <v>9.11313461887236</v>
       </c>
       <c r="D80" t="n">
-        <v>45.39334263474717</v>
+        <v>7.376418178146415</v>
       </c>
       <c r="E80" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F80" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>85.13198480463875</v>
+        <v>13.8339475307538</v>
       </c>
       <c r="D81" t="n">
-        <v>80.24937151633875</v>
+        <v>13.04052287140505</v>
       </c>
       <c r="E81" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F81" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3040,16 +3040,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>69.24230644153123</v>
+        <v>11.25187479674882</v>
       </c>
       <c r="D82" t="n">
-        <v>62.91332056518753</v>
+        <v>10.22341459184297</v>
       </c>
       <c r="E82" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F82" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3072,16 +3072,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>84.68063689485405</v>
+        <v>13.76060349541378</v>
       </c>
       <c r="D83" t="n">
-        <v>61.77018338612535</v>
+        <v>10.03765480024537</v>
       </c>
       <c r="E83" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F83" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>62.89873148594496</v>
+        <v>10.22104386646606</v>
       </c>
       <c r="D84" t="n">
-        <v>44.22825894028487</v>
+        <v>7.187092077796292</v>
       </c>
       <c r="E84" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F84" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3136,16 +3136,16 @@
         <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>67.72566635541115</v>
+        <v>11.00542078275431</v>
       </c>
       <c r="D85" t="n">
-        <v>46.13599359872997</v>
+        <v>7.49709895979362</v>
       </c>
       <c r="E85" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F85" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3168,16 +3168,16 @@
         <v>85</v>
       </c>
       <c r="C86" t="n">
-        <v>78.53879653654775</v>
+        <v>12.76255443718901</v>
       </c>
       <c r="D86" t="n">
-        <v>72.52674077630331</v>
+        <v>11.78559537614929</v>
       </c>
       <c r="E86" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F86" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3200,16 +3200,16 @@
         <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>92.7459709807209</v>
+        <v>15.07122028436715</v>
       </c>
       <c r="D87" t="n">
-        <v>69.90073567010738</v>
+        <v>11.35886954639245</v>
       </c>
       <c r="E87" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F87" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3232,16 +3232,16 @@
         <v>87</v>
       </c>
       <c r="C88" t="n">
-        <v>97.29722001509431</v>
+        <v>15.81079825245283</v>
       </c>
       <c r="D88" t="n">
-        <v>74.72000955005623</v>
+        <v>12.14200155188414</v>
       </c>
       <c r="E88" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F88" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3264,16 +3264,16 @@
         <v>88</v>
       </c>
       <c r="C89" t="n">
-        <v>91.17109739492699</v>
+        <v>14.81530332667564</v>
       </c>
       <c r="D89" t="n">
-        <v>85.86624567927144</v>
+        <v>13.95326492288161</v>
       </c>
       <c r="E89" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F89" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3296,16 +3296,16 @@
         <v>89</v>
       </c>
       <c r="C90" t="n">
-        <v>86.59075696570385</v>
+        <v>14.07099800692688</v>
       </c>
       <c r="D90" t="n">
-        <v>80.79144428407696</v>
+        <v>13.12860969616251</v>
       </c>
       <c r="E90" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F90" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3328,16 +3328,16 @@
         <v>90</v>
       </c>
       <c r="C91" t="n">
-        <v>78.80199968010434</v>
+        <v>12.80532494801696</v>
       </c>
       <c r="D91" t="n">
-        <v>56.09583984744561</v>
+        <v>9.115573975209912</v>
       </c>
       <c r="E91" t="n">
-        <v>21.6772757693917</v>
+        <v>3.522557312526152</v>
       </c>
       <c r="F91" t="n">
-        <v>18.45973088497804</v>
+        <v>2.999706268808931</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
